--- a/test/fixtures/proba-import.xlsx
+++ b/test/fixtures/proba-import.xlsx
@@ -43,7 +43,7 @@
     <t>mothers_forename_at_birth</t>
   </si>
   <si>
-    <t>place_of_birth_country_hun</t>
+    <t>place_of_birth_country</t>
   </si>
   <si>
     <t>place_of_birth_locality</t>
@@ -127,7 +127,7 @@
     <t>educational_attainment</t>
   </si>
   <si>
-    <t>professional_qualification_hun</t>
+    <t>professional_qualification</t>
   </si>
   <si>
     <t>mother_tongue</t>
@@ -136,7 +136,7 @@
     <t>speaks_hungarian</t>
   </si>
   <si>
-    <t>previous_country_hun</t>
+    <t>previous_country</t>
   </si>
   <si>
     <t>previous_town</t>
@@ -865,7 +865,7 @@
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="27" customWidth="1"/>
     <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="29" customWidth="1"/>
+    <col min="11" max="11" width="25" customWidth="1"/>
     <col min="12" max="12" width="26" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
@@ -886,10 +886,9 @@
     <col min="36" max="36" width="15" customWidth="1"/>
     <col min="37" max="37" width="20" customWidth="1"/>
     <col min="38" max="38" width="25" customWidth="1"/>
-    <col min="39" max="39" width="30" customWidth="1"/>
+    <col min="39" max="39" width="29" customWidth="1"/>
     <col min="40" max="40" width="16" customWidth="1"/>
-    <col min="41" max="41" width="19" customWidth="1"/>
-    <col min="42" max="42" width="23" customWidth="1"/>
+    <col min="41" max="42" width="19" customWidth="1"/>
     <col min="43" max="43" width="16" customWidth="1"/>
     <col min="44" max="44" width="18" customWidth="1"/>
   </cols>
